--- a/คำนวน GEX 1.xlsx
+++ b/คำนวน GEX 1.xlsx
@@ -19,9 +19,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -123,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -143,9 +143,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -573,7 +575,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4220</v>
+        <v>4195</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
@@ -584,40 +586,40 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4225</v>
+        <v>4200</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4230</v>
+        <v>4205</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4235</v>
+        <v>4210</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4240</v>
+        <v>4215</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>0</v>
@@ -628,329 +630,329 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4245</v>
+        <v>4220</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4250</v>
+        <v>4225</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4255</v>
+        <v>4230</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4260</v>
+        <v>4235</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4265</v>
+        <v>4240</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4270</v>
+        <v>4245</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4275</v>
+        <v>4250</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4280</v>
+        <v>4255</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4285</v>
+        <v>4260</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4290</v>
+        <v>4265</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4295</v>
+        <v>4270</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4300</v>
+        <v>4275</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4305</v>
+        <v>4280</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4310</v>
+        <v>4285</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4315</v>
+        <v>4290</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4320</v>
+        <v>4295</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4325</v>
+        <v>4300</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4330</v>
+        <v>4305</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4335</v>
+        <v>4310</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4340</v>
+        <v>4315</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4345</v>
+        <v>4320</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4350</v>
+        <v>4325</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4355</v>
+        <v>4330</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4360</v>
+        <v>4335</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4365</v>
+        <v>4340</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4370</v>
+        <v>4345</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4375</v>
+        <v>4350</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="n">
-        <v>4380</v>
+        <v>4355</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4385</v>
+        <v>4360</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>4390</v>
+        <v>4365</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0</v>
@@ -958,32 +960,32 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>4395</v>
+        <v>4370</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>4400</v>
+        <v>4375</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>4405</v>
+        <v>4380</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0</v>
@@ -991,10 +993,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>4410</v>
+        <v>4385</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0</v>
@@ -1002,10 +1004,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>4415</v>
+        <v>4390</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0</v>
@@ -1013,32 +1015,32 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>4420</v>
+        <v>4395</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4425</v>
+        <v>4400</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>4430</v>
+        <v>4405</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>0</v>
@@ -1046,21 +1048,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>4435</v>
+        <v>4410</v>
       </c>
       <c r="B45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>4440</v>
+        <v>4415</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0</v>
@@ -1068,10 +1070,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4445</v>
+        <v>4420</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0</v>
@@ -1079,10 +1081,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>4450</v>
+        <v>4425</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0</v>
@@ -1090,10 +1092,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>4455</v>
+        <v>4430</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0</v>
@@ -1101,7 +1103,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>4460</v>
+        <v>4435</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
@@ -1112,10 +1114,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>4465</v>
+        <v>4440</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0</v>
@@ -1123,10 +1125,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>4470</v>
+        <v>4445</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0</v>
@@ -1134,21 +1136,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4475</v>
+        <v>4450</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>4480</v>
+        <v>4455</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0</v>
@@ -1156,7 +1158,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>4485</v>
+        <v>4460</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
@@ -1167,10 +1169,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>4490</v>
+        <v>4465</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0</v>
@@ -1178,7 +1180,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4495</v>
+        <v>4470</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
@@ -1189,10 +1191,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4500</v>
+        <v>4475</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
@@ -1200,7 +1202,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4505</v>
+        <v>4480</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
@@ -1211,10 +1213,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4510</v>
+        <v>4485</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0</v>
@@ -1222,7 +1224,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4515</v>
+        <v>4490</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
@@ -1233,7 +1235,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4520</v>
+        <v>4495</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
@@ -1244,10 +1246,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>4525</v>
+        <v>4500</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0</v>
@@ -1255,7 +1257,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>4530</v>
+        <v>4505</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
@@ -1266,7 +1268,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>4535</v>
+        <v>4510</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
@@ -1277,7 +1279,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>4540</v>
+        <v>4515</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
@@ -1288,7 +1290,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>4545</v>
+        <v>4520</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
@@ -1299,10 +1301,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>4550</v>
+        <v>4525</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0</v>
@@ -1310,7 +1312,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>4555</v>
+        <v>4530</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
@@ -1321,7 +1323,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>4560</v>
+        <v>4535</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
@@ -1332,7 +1334,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>4565</v>
+        <v>4540</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
@@ -1343,7 +1345,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>4570</v>
+        <v>4545</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
@@ -1354,7 +1356,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>4575</v>
+        <v>4550</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>1</v>
@@ -1365,7 +1367,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>4580</v>
+        <v>4555</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
@@ -4938,7 +4940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5002,7 +5004,7 @@
           <t>G4TU6</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="14" t="n">
         <v>4390.7</v>
       </c>
       <c r="D2" s="12" t="n">
@@ -5025,8 +5027,78 @@
       <c r="I2" s="12" t="n">
         <v>4425</v>
       </c>
-      <c r="J2" s="13" t="n">
-        <v>46286.90754090722</v>
+      <c r="J2" s="15" t="n">
+        <v>46286.90754090278</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OG4U6</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>4318.4</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>376</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>578</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>-202</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Negative GEX (แกว่งแรง)</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="12" t="n">
+        <v>4300</v>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>46289.81005099537</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G4MU6</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>488</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>486</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Positive GEX (นิ่ง)</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>4475</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>4325</v>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>46292.67314317612</v>
       </c>
     </row>
   </sheetData>

--- a/คำนวน GEX 1.xlsx
+++ b/คำนวน GEX 1.xlsx
@@ -5098,7 +5098,7 @@
         <v>4325</v>
       </c>
       <c r="J4" s="15" t="n">
-        <v>46292.67314317612</v>
+        <v>46292.69555492327</v>
       </c>
     </row>
   </sheetData>

--- a/คำนวน GEX 1.xlsx
+++ b/คำนวน GEX 1.xlsx
@@ -5098,7 +5098,7 @@
         <v>4325</v>
       </c>
       <c r="J4" s="15" t="n">
-        <v>46292.69555492327</v>
+        <v>46292.78729457529</v>
       </c>
     </row>
   </sheetData>
